--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/GANDAKI_Datenbank/after_conversion_gandaki_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/GANDAKI_Datenbank/after_conversion_gandaki_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="55">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Bahun Danda, Lamjung</t>
@@ -539,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:AE13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -566,9 +569,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -659,13 +663,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2">
         <v>28.34135</v>
@@ -719,12 +726,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3">
         <v>28.41303</v>
@@ -778,12 +785,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4">
         <v>28.55369</v>
@@ -837,12 +844,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5">
         <v>28.30561</v>
@@ -896,12 +903,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6">
         <v>28.42176</v>
@@ -949,12 +956,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7">
         <v>28.4594</v>
@@ -1008,12 +1015,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8">
         <v>28.47828</v>
@@ -1064,12 +1071,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9">
         <v>28.49626</v>
@@ -1123,12 +1130,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10">
         <v>28.45786</v>
@@ -1182,12 +1189,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11">
         <v>28.45316</v>
@@ -1232,12 +1239,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12">
         <v>28.45316</v>
@@ -1282,12 +1289,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13">
         <v>28.36776</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/GANDAKI_Datenbank/after_conversion_gandaki_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/GANDAKI_Datenbank/after_conversion_gandaki_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="56">
   <si>
     <t>location</t>
   </si>
@@ -179,6 +179,9 @@
   </si>
   <si>
     <t>S12</t>
+  </si>
+  <si>
+    <t>Metamorphic Rock</t>
   </si>
 </sst>
 </file>
@@ -550,7 +553,7 @@
     <col min="3" max="3" width="16.7109375" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="18.7109375" customWidth="1"/>
     <col min="9" max="9" width="38.7109375" customWidth="1"/>
@@ -680,6 +683,9 @@
       <c r="D2">
         <v>84.40621</v>
       </c>
+      <c r="F2" t="s">
+        <v>55</v>
+      </c>
       <c r="H2">
         <v>47.1</v>
       </c>
@@ -739,6 +745,9 @@
       <c r="D3">
         <v>84.40649000000001</v>
       </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
       <c r="H3">
         <v>36.6</v>
       </c>
@@ -798,6 +807,9 @@
       <c r="D4">
         <v>84.25097</v>
       </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
       <c r="H4">
         <v>57</v>
       </c>
@@ -857,6 +869,9 @@
       <c r="D5">
         <v>83.94889999999999</v>
       </c>
+      <c r="F5" t="s">
+        <v>55</v>
+      </c>
       <c r="H5">
         <v>31.6</v>
       </c>
@@ -916,6 +931,9 @@
       <c r="D6">
         <v>83.82062000000001</v>
       </c>
+      <c r="F6" t="s">
+        <v>55</v>
+      </c>
       <c r="H6">
         <v>40.1</v>
       </c>
@@ -969,6 +987,9 @@
       <c r="D7">
         <v>83.62718</v>
       </c>
+      <c r="F7" t="s">
+        <v>55</v>
+      </c>
       <c r="H7">
         <v>53.9</v>
       </c>
@@ -1028,6 +1049,9 @@
       <c r="D8">
         <v>83.64129</v>
       </c>
+      <c r="F8" t="s">
+        <v>55</v>
+      </c>
       <c r="H8">
         <v>54.4</v>
       </c>
@@ -1084,6 +1108,9 @@
       <c r="D9">
         <v>83.65428</v>
       </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
       <c r="H9">
         <v>62.8</v>
       </c>
@@ -1143,6 +1170,9 @@
       <c r="D10">
         <v>83.62614000000001</v>
       </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
       <c r="H10">
         <v>64.3</v>
       </c>
@@ -1202,6 +1232,9 @@
       <c r="D11">
         <v>83.51419</v>
       </c>
+      <c r="F11" t="s">
+        <v>55</v>
+      </c>
       <c r="H11">
         <v>52.7</v>
       </c>
@@ -1252,6 +1285,9 @@
       <c r="D12">
         <v>83.51419</v>
       </c>
+      <c r="F12" t="s">
+        <v>55</v>
+      </c>
       <c r="H12">
         <v>47.9</v>
       </c>
@@ -1301,6 +1337,9 @@
       </c>
       <c r="D13">
         <v>83.5025</v>
+      </c>
+      <c r="F13" t="s">
+        <v>55</v>
       </c>
       <c r="H13">
         <v>52.5</v>
